--- a/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-30T11:02:30+00:00</t>
+    <t>2023-11-06T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1127,7 +1127,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="INS-C"/&gt;
     &lt;display value="INS calculé"/&gt;
   &lt;/coding&gt;
@@ -1288,14 +1288,14 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="NDP"/&gt;
     &lt;display value="Identifiant au dossier pharmaceutique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NDP.system</t>
@@ -1429,7 +1429,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="INS-NIR"/&gt;
     &lt;display value="NIR"/&gt;
   &lt;/coding&gt;
@@ -1480,7 +1480,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="INS-NIA"/&gt;
     &lt;display value="NIA"/&gt;
   &lt;/coding&gt;
@@ -3023,7 +3023,7 @@
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.4140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.37109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="21.17578125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>

--- a/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:08:49+00:00</t>
+    <t>2023-11-07T10:16:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:16:09+00:00</t>
+    <t>2023-11-07T10:18:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:18:25+00:00</t>
+    <t>2023-11-07T10:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:25:25+00:00</t>
+    <t>2023-11-07T10:39:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:39:28+00:00</t>
+    <t>2023-11-07T10:47:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:47:16+00:00</t>
+    <t>2023-11-07T10:49:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
